--- a/dcf/NBIS.xlsx
+++ b/dcf/NBIS.xlsx
@@ -844,7 +844,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1126,25 +1126,25 @@
         <v>9</v>
       </c>
       <c r="B5" s="53" t="n">
-        <v>35.91253571612525</v>
+        <v>1.851393571213226</v>
       </c>
       <c r="C5" s="53" t="n">
-        <v>32.73947133872856</v>
+        <v>0.4988721911021091</v>
       </c>
       <c r="D5" s="53" t="n">
-        <v>29.75171981803452</v>
+        <v>-0.7652773200813359</v>
       </c>
       <c r="E5" s="53" t="n">
-        <v>26.93858383205511</v>
+        <v>-1.94632969864901</v>
       </c>
       <c r="F5" s="53" t="n">
-        <v>24.29001071243052</v>
+        <v>-3.049237213612757</v>
       </c>
       <c r="G5" s="53" t="n">
-        <v>21.79655140587773</v>
+        <v>-4.078650347159492</v>
       </c>
       <c r="H5" s="53" t="n">
-        <v>19.44932220052621</v>
+        <v>-5.038937075875255</v>
       </c>
     </row>
     <row r="6">
@@ -1152,25 +1152,25 @@
         <v>10</v>
       </c>
       <c r="B6" s="53" t="n">
-        <v>47.24283161172686</v>
+        <v>7.643424608925435</v>
       </c>
       <c r="C6" s="53" t="n">
-        <v>43.55743406938567</v>
+        <v>6.028999248516689</v>
       </c>
       <c r="D6" s="53" t="n">
-        <v>40.08271762798358</v>
+        <v>4.515913967163913</v>
       </c>
       <c r="E6" s="53" t="n">
-        <v>36.80662082272529</v>
+        <v>3.098196680705452</v>
       </c>
       <c r="F6" s="53" t="n">
-        <v>33.7178059545789</v>
+        <v>1.770238214289956</v>
       </c>
       <c r="G6" s="53" t="n">
-        <v>30.80561313278444</v>
+        <v>0.5267691073461342</v>
       </c>
       <c r="H6" s="53" t="n">
-        <v>28.06001740848612</v>
+        <v>-0.637162015424784</v>
       </c>
     </row>
     <row r="7">
@@ -1178,25 +1178,25 @@
         <v>11</v>
       </c>
       <c r="B7" s="53" t="n">
-        <v>58.57312750732849</v>
+        <v>13.43545564663764</v>
       </c>
       <c r="C7" s="53" t="n">
-        <v>54.37539680004274</v>
+        <v>11.55912630593126</v>
       </c>
       <c r="D7" s="53" t="n">
-        <v>50.41371543793265</v>
+        <v>9.797105254409162</v>
       </c>
       <c r="E7" s="53" t="n">
-        <v>46.67465781339547</v>
+        <v>8.142723060059904</v>
       </c>
       <c r="F7" s="53" t="n">
-        <v>43.14560119672728</v>
+        <v>6.589713642192664</v>
       </c>
       <c r="G7" s="53" t="n">
-        <v>39.81467485969117</v>
+        <v>5.132188561851761</v>
       </c>
       <c r="H7" s="53" t="n">
-        <v>36.67071261644602</v>
+        <v>3.764613045025693</v>
       </c>
     </row>
     <row r="8">
@@ -1204,25 +1204,25 @@
         <v>12</v>
       </c>
       <c r="B8" s="53" t="n">
-        <v>69.9034234029301</v>
+        <v>19.22748668434985</v>
       </c>
       <c r="C8" s="53" t="n">
-        <v>65.19335953069984</v>
+        <v>17.08925336334582</v>
       </c>
       <c r="D8" s="53" t="n">
-        <v>60.7447132478817</v>
+        <v>15.07829654165439</v>
       </c>
       <c r="E8" s="54" t="n">
-        <v>56.54269480406565</v>
+        <v>13.18724943941436</v>
       </c>
       <c r="F8" s="53" t="n">
-        <v>52.57339643887565</v>
+        <v>11.40918907009537</v>
       </c>
       <c r="G8" s="53" t="n">
-        <v>48.8237365865979</v>
+        <v>9.737608016357376</v>
       </c>
       <c r="H8" s="53" t="n">
-        <v>45.28140782440593</v>
+        <v>8.166388105476157</v>
       </c>
     </row>
     <row r="9">
@@ -1230,25 +1230,25 @@
         <v>13</v>
       </c>
       <c r="B9" s="53" t="n">
-        <v>81.23371929853174</v>
+        <v>25.01951772206205</v>
       </c>
       <c r="C9" s="53" t="n">
-        <v>76.01132226135694</v>
+        <v>22.61938042076039</v>
       </c>
       <c r="D9" s="53" t="n">
-        <v>71.07571105783077</v>
+        <v>20.35948782889964</v>
       </c>
       <c r="E9" s="53" t="n">
-        <v>66.41073179473582</v>
+        <v>18.23177581876881</v>
       </c>
       <c r="F9" s="53" t="n">
-        <v>62.00119168102403</v>
+        <v>16.22866449799806</v>
       </c>
       <c r="G9" s="53" t="n">
-        <v>57.83279831350463</v>
+        <v>14.343027470863</v>
       </c>
       <c r="H9" s="53" t="n">
-        <v>53.89210303236582</v>
+        <v>12.56816316592662</v>
       </c>
     </row>
     <row r="10">
@@ -1256,25 +1256,25 @@
         <v>14</v>
       </c>
       <c r="B10" s="53" t="n">
-        <v>92.5640151941333</v>
+        <v>30.81154875977426</v>
       </c>
       <c r="C10" s="53" t="n">
-        <v>86.82928499201401</v>
+        <v>28.14950747817497</v>
       </c>
       <c r="D10" s="53" t="n">
-        <v>81.40670886777978</v>
+        <v>25.64067911614488</v>
       </c>
       <c r="E10" s="53" t="n">
-        <v>76.27876878540599</v>
+        <v>23.27630219812326</v>
       </c>
       <c r="F10" s="53" t="n">
-        <v>71.4289869231724</v>
+        <v>21.04813992590078</v>
       </c>
       <c r="G10" s="53" t="n">
-        <v>66.84186004041132</v>
+        <v>18.94844692536862</v>
       </c>
       <c r="H10" s="53" t="n">
-        <v>62.50279824032571</v>
+        <v>16.9699382263771</v>
       </c>
     </row>
     <row r="11">
@@ -1282,25 +1282,25 @@
         <v>15</v>
       </c>
       <c r="B11" s="53" t="n">
-        <v>103.894311089735</v>
+        <v>36.60357979748648</v>
       </c>
       <c r="C11" s="53" t="n">
-        <v>97.64724772267111</v>
+        <v>33.67963453558954</v>
       </c>
       <c r="D11" s="53" t="n">
-        <v>91.73770667772887</v>
+        <v>30.92187040339013</v>
       </c>
       <c r="E11" s="53" t="n">
-        <v>86.14680577607615</v>
+        <v>28.32082857747772</v>
       </c>
       <c r="F11" s="53" t="n">
-        <v>80.85678216532077</v>
+        <v>25.86761535380349</v>
       </c>
       <c r="G11" s="53" t="n">
-        <v>75.85092176731807</v>
+        <v>23.55386637987425</v>
       </c>
       <c r="H11" s="53" t="n">
-        <v>71.11349344828561</v>
+        <v>21.37171328682757</v>
       </c>
     </row>
     <row r="13">
@@ -1666,7 +1666,7 @@
         </is>
       </c>
       <c r="I8" s="48" t="n">
-        <v>1.013890290831205</v>
+        <v>1.059379288306961</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24415,7 +24415,7 @@
         </is>
       </c>
       <c r="B49" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -24567,13 +24567,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>56.54269480406565</v>
+        <v>13.18724943941436</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>99.27452051421568</v>
+        <v>33.67697807801991</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>23.60532349621339</v>
+        <v>-2.836053350402056</v>
       </c>
     </row>
     <row r="59">
